--- a/artfynd/A 29988-2025 artfynd.xlsx
+++ b/artfynd/A 29988-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15283573</v>
+        <v>2374000</v>
       </c>
       <c r="B2" t="n">
-        <v>44175</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102421</v>
+        <v>219955</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(von Heyden, 1863)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>700 m S Botillabo, Sm</t>
+          <t>600 m S Botillabo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541658.2719380566</v>
+        <v>541679</v>
       </c>
       <c r="R2" t="n">
-        <v>6315897.688327075</v>
+        <v>6315888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +757,9 @@
           <t>2012-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -807,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2374010</v>
+        <v>2374001</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -861,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541658.2719380566</v>
+        <v>541658</v>
       </c>
       <c r="R3" t="n">
-        <v>6315897.688327075</v>
+        <v>6315898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,19 +878,9 @@
           <t>2012-07-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -940,6 +914,127 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2374002</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>600 m S Botillabo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>541568</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6315907</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ledningsgata</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Längs grusväg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helena Lager</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
